--- a/docs/workbook-split/dateien/Kalkulation.xlsx
+++ b/docs/workbook-split/dateien/Kalkulation.xlsx
@@ -656,9 +656,8 @@
           <t>Material gesamt</t>
         </is>
       </c>
-      <c r="H7" s="7">
-        <f>SUM(D7:D8)</f>
-        <v/>
+      <c r="H7" s="7" t="n">
+        <v>80.20999999999999</v>
       </c>
       <c r="I7" s="1" t="n"/>
       <c r="J7" s="1" t="n"/>
@@ -684,9 +683,8 @@
           <t>Material-Gemeinkosten</t>
         </is>
       </c>
-      <c r="H8" s="7">
-        <f>H7*D9</f>
-        <v/>
+      <c r="H8" s="7" t="n">
+        <v>5.53449</v>
       </c>
       <c r="I8" s="1" t="n"/>
       <c r="J8" s="1" t="n"/>
@@ -712,9 +710,8 @@
           <t>Fertigung gesamt</t>
         </is>
       </c>
-      <c r="H9" s="7">
-        <f>SUM(D11:D12)</f>
-        <v/>
+      <c r="H9" s="7" t="n">
+        <v>36.8</v>
       </c>
       <c r="I9" s="1" t="n"/>
       <c r="J9" s="1" t="n"/>
@@ -740,9 +737,8 @@
           <t>Herstellkosten</t>
         </is>
       </c>
-      <c r="H10" s="10">
-        <f>SUM(H7:H9)+D10</f>
-        <v/>
+      <c r="H10" s="10" t="n">
+        <v>123.54449</v>
       </c>
       <c r="I10" s="1" t="n"/>
       <c r="J10" s="1" t="n"/>
@@ -768,9 +764,8 @@
           <t>Vertrieb / Verwaltung</t>
         </is>
       </c>
-      <c r="H11" s="7">
-        <f>H10*D13</f>
-        <v/>
+      <c r="H11" s="7" t="n">
+        <v>18.012786642</v>
       </c>
       <c r="I11" s="1" t="n"/>
       <c r="J11" s="1" t="n"/>
@@ -796,9 +791,8 @@
           <t>Selbstkosten</t>
         </is>
       </c>
-      <c r="H12" s="7">
-        <f>SUM(H10:H11)+D14</f>
-        <v/>
+      <c r="H12" s="7" t="n">
+        <v>142.157276642</v>
       </c>
       <c r="I12" s="1" t="n"/>
       <c r="J12" s="1" t="n"/>
@@ -824,9 +818,8 @@
           <t>Selbstkosten inkl. Fracht</t>
         </is>
       </c>
-      <c r="H13" s="10">
-        <f>H12+SUM(D15:D16)</f>
-        <v/>
+      <c r="H13" s="10" t="n">
+        <v>145.157276642</v>
       </c>
       <c r="I13" s="1" t="n"/>
       <c r="J13" s="1" t="n"/>
@@ -852,9 +845,8 @@
           <t>Konditionen maximal</t>
         </is>
       </c>
-      <c r="H14" s="11">
-        <f>SUM(D17:D21)+SUM(D23:D24)</f>
-        <v/>
+      <c r="H14" s="11" t="n">
+        <v>0.1138</v>
       </c>
       <c r="I14" s="1" t="n"/>
       <c r="J14" s="1" t="n"/>
@@ -880,9 +872,8 @@
           <t>Konditionen mittel</t>
         </is>
       </c>
-      <c r="H15" s="11">
-        <f>SUM(D17:D20)+D22+SUM(D23:D24)</f>
-        <v/>
+      <c r="H15" s="11" t="n">
+        <v>0.09079999999999999</v>
       </c>
       <c r="I15" s="1" t="n"/>
       <c r="J15" s="1" t="n"/>
@@ -908,9 +899,8 @@
           <t>Limitpreis</t>
         </is>
       </c>
-      <c r="H16" s="10">
-        <f>IF(H14&gt;=1,"n.a.",H13/(1-H14))</f>
-        <v/>
+      <c r="H16" s="10" t="n">
+        <v>163.7974234281201</v>
       </c>
       <c r="I16" s="1" t="n"/>
       <c r="J16" s="1" t="n"/>
@@ -936,9 +926,8 @@
           <t>Risikoaufschläge</t>
         </is>
       </c>
-      <c r="H17" s="7">
-        <f>H13*SUM(D25:D26)</f>
-        <v/>
+      <c r="H17" s="7" t="n">
+        <v>5.080504682470001</v>
       </c>
       <c r="I17" s="1" t="n"/>
       <c r="J17" s="1" t="n"/>
@@ -964,9 +953,8 @@
           <t>Gewinn</t>
         </is>
       </c>
-      <c r="H18" s="7">
-        <f>H13*D27</f>
-        <v/>
+      <c r="H18" s="7" t="n">
+        <v>11.61258213136</v>
       </c>
       <c r="I18" s="1" t="n"/>
       <c r="J18" s="1" t="n"/>
@@ -992,9 +980,8 @@
           <t>Zielpreis</t>
         </is>
       </c>
-      <c r="H19" s="10">
-        <f>IF(H15&gt;=1,"n.a.",SUM(H13,H17:H18)/(1-H15))</f>
-        <v/>
+      <c r="H19" s="10" t="n">
+        <v>178.014038116839</v>
       </c>
       <c r="I19" s="1" t="n"/>
       <c r="J19" s="1" t="n"/>
@@ -1020,9 +1007,8 @@
           <t>Netto-Angebot</t>
         </is>
       </c>
-      <c r="H20" s="10">
-        <f>D28*(1-H15)</f>
-        <v/>
+      <c r="H20" s="10" t="n">
+        <v>159.11</v>
       </c>
       <c r="I20" s="1" t="n"/>
       <c r="J20" s="1" t="n"/>
@@ -1048,9 +1034,8 @@
           <t>DB1</t>
         </is>
       </c>
-      <c r="H21" s="10">
-        <f>H20-H7</f>
-        <v/>
+      <c r="H21" s="10" t="n">
+        <v>78.90000000000002</v>
       </c>
       <c r="I21" s="1" t="n"/>
       <c r="J21" s="1" t="n"/>
@@ -1076,9 +1061,8 @@
           <t>DB1-Marge</t>
         </is>
       </c>
-      <c r="H22" s="11">
-        <f>IF(H20=0,"n.a.",H21/H20)</f>
-        <v/>
+      <c r="H22" s="11" t="n">
+        <v>0.4958833511407204</v>
       </c>
       <c r="I22" s="1" t="n"/>
       <c r="J22" s="1" t="n"/>
@@ -1692,6 +1676,8 @@
       <c r="L60" s="1" t="n"/>
       <c r="M60" s="1" t="n"/>
     </row>
+    <row r="61"/>
+    <row r="62"/>
     <row r="63">
       <c r="C63" t="inlineStr">
         <is>
